--- a/data/trans_dic/IP18A02-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP18A02-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por control de salud periódico</t>
+          <t>Menores que su última consulta al médico fue por control de salud periódico (tasa de respuesta: 98,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,99; 33,26</t>
+          <t>18,47; 33,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,9; 22,03</t>
+          <t>9,39; 22,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,64; 33,76</t>
+          <t>16,58; 32,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,61; 25,86</t>
+          <t>3,93; 25,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,78; 24,3</t>
+          <t>11,86; 25,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,05; 30,8</t>
+          <t>16,17; 30,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,96; 26,96</t>
+          <t>13,91; 26,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,2; 39,92</t>
+          <t>8,41; 39,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,64; 27,02</t>
+          <t>17,08; 26,8</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,5; 25,34</t>
+          <t>14,26; 24,16</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17,79; 27,73</t>
+          <t>17,2; 27,24</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,16; 25,97</t>
+          <t>7,55; 25,92</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,62; 32,28</t>
+          <t>15,84; 30,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,59; 28,4</t>
+          <t>14,47; 28,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,31; 27,27</t>
+          <t>14,74; 27,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,46; 45,25</t>
+          <t>5,62; 44,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,7; 33,79</t>
+          <t>18,01; 32,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,34; 30,02</t>
+          <t>15,42; 29,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,55; 31,08</t>
+          <t>17,1; 30,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,84; 48,08</t>
+          <t>4,09; 44,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,83; 29,9</t>
+          <t>19,03; 29,78</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,21; 26,96</t>
+          <t>17,04; 26,57</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,49; 26,81</t>
+          <t>17,34; 26,89</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,74; 35,44</t>
+          <t>7,72; 37,83</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,5; 31,12</t>
+          <t>14,88; 32,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,05; 24,69</t>
+          <t>11,25; 24,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,93; 29,91</t>
+          <t>11,66; 29,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,13</t>
+          <t>0,0; 60,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,93; 27,89</t>
+          <t>14,0; 27,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,13; 19,49</t>
+          <t>7,48; 20,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,74; 30,71</t>
+          <t>14,6; 31,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,42; 58,73</t>
+          <t>12,46; 56,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,68; 27,04</t>
+          <t>15,86; 27,22</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,93; 19,91</t>
+          <t>10,84; 19,74</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,87; 27,33</t>
+          <t>15,46; 27,32</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,48; 49,13</t>
+          <t>11,06; 49,93</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,93; 31,58</t>
+          <t>21,17; 31,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,55; 28,32</t>
+          <t>18,23; 28,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,44; 22,1</t>
+          <t>13,64; 21,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,62; 35,69</t>
+          <t>9,28; 34,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,25; 26,77</t>
+          <t>17,32; 27,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,0; 27,16</t>
+          <t>17,97; 27,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,22; 21,09</t>
+          <t>12,11; 21,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,8; 31,54</t>
+          <t>11,86; 31,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,64; 27,92</t>
+          <t>20,52; 27,98</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,31; 26,17</t>
+          <t>19,14; 25,98</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,36; 20,19</t>
+          <t>13,8; 20,13</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,71; 29,29</t>
+          <t>12,84; 28,52</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,34; 31,0</t>
+          <t>16,02; 31,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,03; 27,64</t>
+          <t>16,18; 27,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,25; 22,74</t>
+          <t>11,87; 22,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,25; 43,77</t>
+          <t>9,76; 42,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,97; 21,56</t>
+          <t>9,97; 22,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,19; 20,2</t>
+          <t>9,42; 19,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,6; 24,11</t>
+          <t>12,99; 24,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,76; 26,18</t>
+          <t>6,39; 26,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,07; 23,33</t>
+          <t>14,12; 22,86</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14,09; 22,08</t>
+          <t>14,33; 21,7</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13,81; 21,65</t>
+          <t>13,54; 21,77</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,52; 27,89</t>
+          <t>10,38; 28,17</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,44; 29,33</t>
+          <t>13,59; 28,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,39; 38,44</t>
+          <t>16,78; 37,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,99; 33,81</t>
+          <t>15,54; 33,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,51</t>
+          <t>0,0; 45,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,46; 25,78</t>
+          <t>11,09; 26,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,14; 27,23</t>
+          <t>11,82; 27,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,81; 33,05</t>
+          <t>14,23; 32,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,72</t>
+          <t>0,0; 41,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,3; 25,25</t>
+          <t>13,66; 25,24</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16,53; 28,53</t>
+          <t>17,0; 28,83</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17,43; 29,76</t>
+          <t>17,45; 30,79</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,18; 28,6</t>
+          <t>3,07; 31,7</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>21,19; 26,77</t>
+          <t>21,31; 27,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,41; 23,78</t>
+          <t>18,29; 23,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16,95; 21,93</t>
+          <t>17,21; 22,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,3; 24,92</t>
+          <t>12,16; 25,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,56; 22,54</t>
+          <t>17,21; 22,21</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,76; 21,95</t>
+          <t>16,8; 21,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,09; 22,12</t>
+          <t>17,0; 22,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,44; 25,26</t>
+          <t>13,74; 24,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19,89; 23,98</t>
+          <t>19,93; 23,72</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18,24; 21,96</t>
+          <t>18,09; 22,0</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17,78; 21,28</t>
+          <t>17,72; 21,3</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,43; 22,93</t>
+          <t>14,53; 22,81</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que su última consulta al médico fue por control de salud periódico (tasa de respuesta: 98,79%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>23874</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11840</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>18466</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2739</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>15073</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>19564</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>18338</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>4131</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>38946</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>31404</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>36804</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>6871</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>17453; 31256</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7661; 18011</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12490; 24749</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>974; 6218</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>10209; 21584</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>13996; 26494</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>12929; 24796</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1728; 8054</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>30847; 48409</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>23964; 40609</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>28953; 45849</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3421; 11744</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>19049</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18668</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>19671</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2054</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>18591</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>19796</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>22929</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2961</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>37640</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>38464</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>42600</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>5015</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>12719; 24581</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>13016; 25625</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>14288; 26666</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>589; 4692</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>13577; 24615</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>13717; 26286</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>16858; 30265</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>662; 7142</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>29621; 46360</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>30480; 47533</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>33902; 52577</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2061; 10096</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>13434</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>13732</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>518</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>17211</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>10708</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>14846</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>3359</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>30645</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>24440</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>25249</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3878</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>8944; 19388</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9010; 19740</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6165; 15437</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2070</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>11971; 23931</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>6211; 16601</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>9856; 21060</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1361; 6227</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>23091; 39629</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>17674; 32192</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>18612; 32894</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1587; 7160</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>44866</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>44423</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>36058</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6268</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>38860</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>47662</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>30663</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>8133</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>83726</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>92085</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>66721</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>14401</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>36500; 54981</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>35066; 54235</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>28090; 44502</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2803; 10322</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>30564; 48613</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>38731; 58954</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>22740; 39587</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>4879; 13097</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>71588; 97632</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>78086; 105985</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>54350; 79265</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>9158; 20342</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>19477</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>28995</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>20514</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>4563</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>15464</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>19475</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>23185</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>4329</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>34941</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>48470</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>43699</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>8892</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>13751; 26880</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>21942; 37554</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>14555; 27691</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1994; 8688</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>10243; 22628</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>12549; 26538</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>16684; 30928</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1910; 7913</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>26623; 43109</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>38524; 58351</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>33998; 54660</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>5226; 14182</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>14130</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>14185</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>13368</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1451</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>11876</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>12983</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>13937</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1472</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>26006</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>27168</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>27305</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>2923</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>9346; 19870</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>8837; 19859</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>8749; 18673</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4295</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>7363; 17342</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>8216; 19322</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>8676; 19661</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4830</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>18461; 34118</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>20769; 35226</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>20464; 36110</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>645; 6667</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>134830</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>131844</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>118480</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>17594</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>117075</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>130188</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>123898</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>24386</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>251905</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>262032</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>242378</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>41980</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>119742; 153487</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>115633; 147961</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>104984; 134965</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>12002; 25058</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>101967; 131582</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>113686; 148289</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>108144; 140812</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>17912; 32499</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>230074; 273861</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>236820; 287930</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>220884; 265410</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>33279; 52240</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP18A02-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP18A02-Clase-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,47; 33,07</t>
+          <t>18,19; 32,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,39; 22,08</t>
+          <t>8,88; 22,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,58; 32,85</t>
+          <t>17,49; 34,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,93; 25,1</t>
+          <t>4,01; 25,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,86; 25,06</t>
+          <t>11,51; 25,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,17; 30,62</t>
+          <t>15,75; 30,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,91; 26,68</t>
+          <t>13,57; 27,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,41; 39,22</t>
+          <t>7,82; 39,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,08; 26,8</t>
+          <t>16,37; 26,85</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,26; 24,16</t>
+          <t>14,09; 23,92</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17,2; 27,24</t>
+          <t>17,16; 27,24</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,55; 25,92</t>
+          <t>7,56; 26,25</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,84; 30,62</t>
+          <t>17,0; 31,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,47; 28,49</t>
+          <t>14,25; 28,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,74; 27,51</t>
+          <t>14,09; 27,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,62; 44,72</t>
+          <t>5,8; 48,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,01; 32,66</t>
+          <t>17,77; 33,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,42; 29,55</t>
+          <t>15,9; 30,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,1; 30,69</t>
+          <t>16,89; 30,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,09; 44,1</t>
+          <t>3,86; 44,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,03; 29,78</t>
+          <t>18,96; 30,22</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,04; 26,57</t>
+          <t>16,7; 26,53</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,34; 26,89</t>
+          <t>17,49; 27,13</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,72; 37,83</t>
+          <t>7,73; 38,17</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,88; 32,27</t>
+          <t>14,87; 32,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,25; 24,65</t>
+          <t>10,8; 25,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,66; 29,18</t>
+          <t>11,92; 29,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,63</t>
+          <t>0,0; 70,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,0; 27,99</t>
+          <t>13,72; 27,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,48; 20,0</t>
+          <t>7,82; 20,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,6; 31,2</t>
+          <t>14,8; 30,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,46; 56,99</t>
+          <t>11,23; 57,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,86; 27,22</t>
+          <t>15,98; 26,78</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,84; 19,74</t>
+          <t>10,9; 19,95</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,46; 27,32</t>
+          <t>15,36; 27,21</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,06; 49,93</t>
+          <t>12,16; 50,89</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,17; 31,89</t>
+          <t>20,96; 31,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,23; 28,2</t>
+          <t>18,14; 28,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,64; 21,61</t>
+          <t>13,4; 22,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,28; 34,18</t>
+          <t>11,04; 36,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,32; 27,55</t>
+          <t>17,27; 27,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,97; 27,35</t>
+          <t>18,02; 27,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,11; 21,08</t>
+          <t>12,28; 21,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,86; 31,84</t>
+          <t>11,75; 31,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,52; 27,98</t>
+          <t>20,61; 28,19</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,14; 25,98</t>
+          <t>19,2; 26,11</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,8; 20,13</t>
+          <t>13,82; 20,28</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,84; 28,52</t>
+          <t>13,49; 29,26</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,02; 31,32</t>
+          <t>15,65; 30,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,18; 27,69</t>
+          <t>16,16; 27,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,87; 22,58</t>
+          <t>12,01; 22,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,76; 42,5</t>
+          <t>10,2; 43,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,97; 22,03</t>
+          <t>9,98; 21,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,42; 19,92</t>
+          <t>9,96; 20,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,99; 24,09</t>
+          <t>12,44; 24,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,39; 26,46</t>
+          <t>6,37; 25,77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,12; 22,86</t>
+          <t>14,15; 23,21</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14,33; 21,7</t>
+          <t>14,54; 22,58</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13,54; 21,77</t>
+          <t>13,85; 21,92</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,38; 28,17</t>
+          <t>10,18; 27,98</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,59; 28,89</t>
+          <t>13,77; 28,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16,78; 37,71</t>
+          <t>18,37; 38,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,54; 33,16</t>
+          <t>15,03; 33,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,91</t>
+          <t>0,0; 43,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,09; 26,13</t>
+          <t>11,15; 26,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,82; 27,8</t>
+          <t>11,89; 26,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,23; 32,25</t>
+          <t>14,3; 32,14</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,39</t>
+          <t>0,0; 36,95</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,66; 25,24</t>
+          <t>14,27; 25,35</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17,0; 28,83</t>
+          <t>16,07; 28,81</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17,45; 30,79</t>
+          <t>17,79; 29,45</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,07; 31,7</t>
+          <t>4,03; 29,36</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>21,31; 27,31</t>
+          <t>21,39; 26,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,29; 23,4</t>
+          <t>18,29; 23,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,21; 22,12</t>
+          <t>17,04; 22,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,16; 25,39</t>
+          <t>12,33; 25,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,21; 22,21</t>
+          <t>17,35; 22,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,8; 21,91</t>
+          <t>16,75; 21,78</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,0; 22,13</t>
+          <t>16,8; 22,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,74; 24,93</t>
+          <t>12,87; 25,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19,93; 23,72</t>
+          <t>20,02; 23,99</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18,09; 22,0</t>
+          <t>18,15; 21,89</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17,72; 21,3</t>
+          <t>17,61; 21,31</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,53; 22,81</t>
+          <t>14,36; 22,77</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17453; 31256</t>
+          <t>17190; 30725</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7661; 18011</t>
+          <t>7241; 18100</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12490; 24749</t>
+          <t>13179; 26102</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>974; 6218</t>
+          <t>993; 6267</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10209; 21584</t>
+          <t>9914; 21538</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13996; 26494</t>
+          <t>13628; 26406</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12929; 24796</t>
+          <t>12618; 25105</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1728; 8054</t>
+          <t>1605; 8040</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>30847; 48409</t>
+          <t>29563; 48490</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23964; 40609</t>
+          <t>23683; 40201</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28953; 45849</t>
+          <t>28878; 45846</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3421; 11744</t>
+          <t>3424; 11895</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12719; 24581</t>
+          <t>13649; 25307</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13016; 25625</t>
+          <t>12815; 25363</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14288; 26666</t>
+          <t>13657; 26835</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>589; 4692</t>
+          <t>608; 5116</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13577; 24615</t>
+          <t>13392; 25446</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13717; 26286</t>
+          <t>14147; 27512</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16858; 30265</t>
+          <t>16650; 29989</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>662; 7142</t>
+          <t>625; 7144</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29621; 46360</t>
+          <t>29516; 47038</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30480; 47533</t>
+          <t>29879; 47463</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33902; 52577</t>
+          <t>34190; 53054</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2061; 10096</t>
+          <t>2063; 10186</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8944; 19388</t>
+          <t>8933; 19520</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9010; 19740</t>
+          <t>8650; 20280</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6165; 15437</t>
+          <t>6304; 15496</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 2070</t>
+          <t>0; 2418</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11971; 23931</t>
+          <t>11729; 23923</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6211; 16601</t>
+          <t>6491; 17089</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9856; 21060</t>
+          <t>9987; 20766</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1361; 6227</t>
+          <t>1227; 6304</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>23091; 39629</t>
+          <t>23261; 38991</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17674; 32192</t>
+          <t>17777; 32537</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18612; 32894</t>
+          <t>18499; 32765</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1587; 7160</t>
+          <t>1743; 7298</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>36500; 54981</t>
+          <t>36150; 53980</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>35066; 54235</t>
+          <t>34886; 55444</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28090; 44502</t>
+          <t>27587; 45467</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2803; 10322</t>
+          <t>3335; 10951</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30564; 48613</t>
+          <t>30472; 47729</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38731; 58954</t>
+          <t>38837; 58541</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22740; 39587</t>
+          <t>23062; 39560</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4879; 13097</t>
+          <t>4834; 12939</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>71588; 97632</t>
+          <t>71897; 98342</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>78086; 105985</t>
+          <t>78300; 106503</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>54350; 79265</t>
+          <t>54404; 79866</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9158; 20342</t>
+          <t>9622; 20874</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13751; 26880</t>
+          <t>13434; 26159</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>21942; 37554</t>
+          <t>21910; 37835</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14555; 27691</t>
+          <t>14728; 27984</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1994; 8688</t>
+          <t>2085; 8848</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10243; 22628</t>
+          <t>10248; 21717</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12549; 26538</t>
+          <t>13276; 27294</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16684; 30928</t>
+          <t>15971; 30833</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1910; 7913</t>
+          <t>1903; 7704</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>26623; 43109</t>
+          <t>26671; 43762</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>38524; 58351</t>
+          <t>39086; 60705</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>33998; 54660</t>
+          <t>34766; 55024</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5226; 14182</t>
+          <t>5127; 14088</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9346; 19870</t>
+          <t>9471; 19753</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8837; 19859</t>
+          <t>9673; 20110</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8749; 18673</t>
+          <t>8464; 19132</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 4295</t>
+          <t>0; 4035</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7363; 17342</t>
+          <t>7401; 17623</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8216; 19322</t>
+          <t>8265; 18585</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8676; 19661</t>
+          <t>8719; 19592</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 4830</t>
+          <t>0; 4312</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>18461; 34118</t>
+          <t>19283; 34262</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>20769; 35226</t>
+          <t>19631; 35200</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>20464; 36110</t>
+          <t>20858; 34537</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>645; 6667</t>
+          <t>848; 6174</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>119742; 153487</t>
+          <t>120188; 151149</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>115633; 147961</t>
+          <t>115642; 149401</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>104984; 134965</t>
+          <t>103932; 134314</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12002; 25058</t>
+          <t>12163; 24991</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>101967; 131582</t>
+          <t>102815; 134049</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>113686; 148289</t>
+          <t>113380; 147430</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>108144; 140812</t>
+          <t>106878; 140542</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>17912; 32499</t>
+          <t>16772; 32749</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>230074; 273861</t>
+          <t>231118; 276975</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>236820; 287930</t>
+          <t>237633; 286527</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>220884; 265410</t>
+          <t>219462; 265619</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>33279; 52240</t>
+          <t>32890; 52155</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP18A02-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP18A02-Clase-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por control de salud periódico (tasa de respuesta: 98,79%)</t>
+          <t>Menores cuya última consulta médica fue por control de salud periódico (tasa de respuesta: 98,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>17,5%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>22,61%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19,73%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>21,44%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>25,26%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>14,52%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>24,51%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11,06%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>17,5%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>22,61%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>19,73%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,19; 32,51</t>
+          <t>11,78; 24,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,88; 22,19</t>
+          <t>16,05; 30,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,49; 34,64</t>
+          <t>13,96; 26,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,01; 25,3</t>
+          <t>8,75; 42,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,51; 25,01</t>
+          <t>18,99; 33,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,75; 30,52</t>
+          <t>8,9; 22,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,57; 27,01</t>
+          <t>17,64; 33,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,82; 39,15</t>
+          <t>4,13; 29,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,37; 26,85</t>
+          <t>16,64; 27,02</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,09; 23,92</t>
+          <t>14,5; 25,34</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17,16; 27,24</t>
+          <t>17,79; 27,73</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,56; 26,25</t>
+          <t>7,89; 28,08</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>24,67%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>22,25%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>23,25%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>19,28%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>23,73%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>20,75%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>20,29%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>19,58%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>24,67%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>22,25%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>23,25%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,61%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,0; 31,52</t>
+          <t>17,7; 33,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,25; 28,19</t>
+          <t>15,34; 30,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,09; 27,68</t>
+          <t>16,55; 31,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,8; 48,77</t>
+          <t>3,83; 50,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,77; 33,76</t>
+          <t>16,62; 32,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,9; 30,93</t>
+          <t>14,59; 28,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,89; 30,41</t>
+          <t>14,31; 27,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,86; 44,11</t>
+          <t>5,4; 47,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,96; 30,22</t>
+          <t>18,83; 29,9</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,7; 26,53</t>
+          <t>17,21; 26,96</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,49; 27,13</t>
+          <t>17,49; 26,81</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,73; 38,17</t>
+          <t>8,0; 36,9</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>20,13%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12,9%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>21,99%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>30,51%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>22,36%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>17,15%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>19,67%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>15,18%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>20,13%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>12,9%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>21,99%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,39%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,87; 32,48</t>
+          <t>12,93; 27,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,8; 25,33</t>
+          <t>7,13; 19,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,92; 29,29</t>
+          <t>14,74; 30,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,8</t>
+          <t>11,59; 60,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,72; 27,98</t>
+          <t>14,5; 31,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,82; 20,59</t>
+          <t>11,05; 24,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,8; 30,76</t>
+          <t>11,93; 29,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,23; 57,69</t>
+          <t>0,0; 61,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,98; 26,78</t>
+          <t>15,68; 27,04</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,9; 19,95</t>
+          <t>10,93; 19,91</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,36; 27,21</t>
+          <t>15,87; 27,33</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,16; 50,89</t>
+          <t>10,25; 49,76</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>22,02%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>22,11%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16,33%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>19,87%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>26,02%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>23,1%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>17,51%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>20,75%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>22,02%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>22,11%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16,33%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,96; 31,31</t>
+          <t>17,25; 26,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,14; 28,83</t>
+          <t>18,0; 27,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,4; 22,08</t>
+          <t>12,22; 21,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,04; 36,26</t>
+          <t>10,6; 31,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,27; 27,04</t>
+          <t>20,93; 31,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,02; 27,16</t>
+          <t>18,55; 28,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,28; 21,06</t>
+          <t>13,44; 22,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,75; 31,46</t>
+          <t>13,38; 39,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,61; 28,19</t>
+          <t>20,64; 27,92</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,2; 26,11</t>
+          <t>19,31; 26,17</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,82; 20,28</t>
+          <t>14,36; 20,19</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,49; 29,26</t>
+          <t>14,64; 32,04</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>15,06%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>14,62%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>18,06%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>14,25%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>22,69%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>21,38%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>16,73%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>22,32%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>15,06%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>14,62%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>18,06%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,77%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,65; 30,48</t>
+          <t>9,97; 21,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,16; 27,9</t>
+          <t>10,19; 20,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,01; 22,82</t>
+          <t>12,6; 24,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,2; 43,28</t>
+          <t>6,68; 26,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,98; 21,15</t>
+          <t>16,34; 31,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,96; 20,48</t>
+          <t>16,03; 27,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,44; 24,01</t>
+          <t>11,25; 22,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,37; 25,77</t>
+          <t>9,98; 44,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,15; 23,21</t>
+          <t>14,07; 23,33</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14,54; 22,58</t>
+          <t>14,09; 22,08</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13,85; 21,92</t>
+          <t>13,81; 21,65</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,18; 27,98</t>
+          <t>10,34; 29,03</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>17,89%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>18,68%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>22,86%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>13,76%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>20,55%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>26,94%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>23,74%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>15,51%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>17,89%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>18,68%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>22,86%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,77; 28,72</t>
+          <t>11,46; 25,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,37; 38,19</t>
+          <t>12,14; 27,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,03; 33,98</t>
+          <t>14,81; 33,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,13</t>
+          <t>0,0; 44,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,15; 26,55</t>
+          <t>13,44; 29,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,89; 26,74</t>
+          <t>18,39; 38,44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,3; 32,14</t>
+          <t>15,99; 33,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,95</t>
+          <t>0,0; 44,62</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,27; 25,35</t>
+          <t>14,3; 25,25</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16,07; 28,81</t>
+          <t>16,53; 28,53</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17,79; 29,45</t>
+          <t>17,43; 29,76</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,03; 29,36</t>
+          <t>4,33; 30,77</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>19,76%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>19,24%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>19,47%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>19,1%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>23,99%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>20,86%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>19,42%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>17,83%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>19,76%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>19,24%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>19,47%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>19,07%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>21,39; 26,9</t>
+          <t>17,56; 22,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,29; 23,63</t>
+          <t>16,76; 21,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,04; 22,02</t>
+          <t>17,09; 22,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,33; 25,33</t>
+          <t>13,61; 25,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,35; 22,62</t>
+          <t>21,19; 26,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,75; 21,78</t>
+          <t>18,41; 23,78</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,8; 22,09</t>
+          <t>16,95; 21,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,87; 25,12</t>
+          <t>13,21; 26,68</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20,02; 23,99</t>
+          <t>19,89; 23,98</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18,15; 21,89</t>
+          <t>18,24; 21,96</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17,61; 21,31</t>
+          <t>17,78; 21,28</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,36; 22,77</t>
+          <t>14,96; 24,15</t>
         </is>
       </c>
     </row>
@@ -1669,13 +1669,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por control de salud periódico (tasa de respuesta: 98,79%)</t>
+          <t>Menores cuya última consulta médica fue por control de salud periódico (tasa de respuesta: 98,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>15073</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>19564</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>18338</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4054</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>23874</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>11840</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>18466</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2739</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>15073</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>19564</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>18338</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4131</t>
+          <t>2607</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6871</t>
+          <t>6660</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17190; 30725</t>
+          <t>10148; 20926</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7241; 18100</t>
+          <t>13891; 26652</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13179; 26102</t>
+          <t>12978; 25064</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>993; 6267</t>
+          <t>1653; 8124</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9914; 21538</t>
+          <t>17951; 31435</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13628; 26406</t>
+          <t>7257; 17965</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12618; 25105</t>
+          <t>13292; 25435</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1605; 8040</t>
+          <t>896; 6309</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>29563; 48490</t>
+          <t>30055; 48811</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23683; 40201</t>
+          <t>24374; 42591</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28878; 45846</t>
+          <t>29943; 46676</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3424; 11895</t>
+          <t>3203; 11402</t>
         </is>
       </c>
     </row>
@@ -1999,37 +1999,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2067,44 +2067,44 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>18591</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19796</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>22929</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3042</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>19049</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>18668</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>19671</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>2054</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>18591</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>19796</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>22929</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2961</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
           <t>37640</t>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5015</t>
+          <t>5096</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13649; 25307</t>
+          <t>13336; 25470</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12815; 25363</t>
+          <t>13643; 26707</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13657; 26835</t>
+          <t>16320; 30649</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>608; 5116</t>
+          <t>604; 7959</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13392; 25446</t>
+          <t>13347; 25915</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14147; 27512</t>
+          <t>13124; 25545</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16650; 29989</t>
+          <t>13869; 26434</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>625; 7144</t>
+          <t>552; 4829</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29516; 47038</t>
+          <t>29315; 46534</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29879; 47463</t>
+          <t>30798; 48244</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34190; 53054</t>
+          <t>34206; 52417</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2063; 10186</t>
+          <t>2080; 9590</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>17211</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10708</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>14846</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3006</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>13434</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>13732</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>10403</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>518</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>17211</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>10708</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>14846</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3359</t>
+          <t>436</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3878</t>
+          <t>3442</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8933; 19520</t>
+          <t>11052; 23841</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8650; 20280</t>
+          <t>5920; 16178</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6304; 15496</t>
+          <t>9949; 20731</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 2418</t>
+          <t>1142; 5958</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11729; 23923</t>
+          <t>8711; 18699</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6491; 17089</t>
+          <t>8844; 19765</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9987; 20766</t>
+          <t>6311; 15819</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1227; 6304</t>
+          <t>0; 1964</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>23261; 38991</t>
+          <t>22823; 39368</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17777; 32537</t>
+          <t>17820; 32465</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18499; 32765</t>
+          <t>19111; 32910</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1743; 7298</t>
+          <t>1337; 6490</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>38860</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>47662</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>30663</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>7584</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>44866</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>44423</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>36058</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6268</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>38860</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>47662</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>30663</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>6813</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14401</t>
+          <t>14397</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>36150; 53980</t>
+          <t>30436; 47243</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>34886; 55444</t>
+          <t>38791; 58546</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27587; 45467</t>
+          <t>22950; 39600</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3335; 10951</t>
+          <t>4044; 12178</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30472; 47729</t>
+          <t>36091; 54458</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38837; 58541</t>
+          <t>35678; 54472</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23062; 39560</t>
+          <t>27676; 45520</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4834; 12939</t>
+          <t>3918; 11629</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>71897; 98342</t>
+          <t>72000; 97426</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>78300; 106503</t>
+          <t>78779; 106734</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>54404; 79866</t>
+          <t>56549; 79478</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9622; 20874</t>
+          <t>9877; 21608</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>15464</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>19475</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>23185</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3911</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>19477</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>28995</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>20514</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>4563</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>15464</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>19475</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>23185</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>4507</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8892</t>
+          <t>8418</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13434; 26159</t>
+          <t>10237; 22142</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>21910; 37835</t>
+          <t>13575; 26917</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14728; 27984</t>
+          <t>16183; 30952</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2085; 8848</t>
+          <t>1835; 7378</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10248; 21717</t>
+          <t>14022; 26614</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13276; 27294</t>
+          <t>21743; 37487</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15971; 30833</t>
+          <t>13801; 27887</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1903; 7704</t>
+          <t>1988; 8806</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>26671; 43762</t>
+          <t>26521; 43995</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>39086; 60705</t>
+          <t>37869; 59367</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>34766; 55024</t>
+          <t>34671; 54340</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5127; 14088</t>
+          <t>4895; 13752</t>
         </is>
       </c>
     </row>
@@ -2831,27 +2831,27 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>11876</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>12983</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>13937</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1444</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>14130</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>14185</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>13368</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1451</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>11876</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>12983</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>13937</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>1460</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>2904</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9471; 19753</t>
+          <t>7605; 17114</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9673; 20110</t>
+          <t>8440; 18931</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8464; 19132</t>
+          <t>9032; 20150</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 4035</t>
+          <t>0; 4688</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7401; 17623</t>
+          <t>9244; 20167</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8265; 18585</t>
+          <t>9686; 20241</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8719; 19592</t>
+          <t>9003; 19038</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 4312</t>
+          <t>0; 4277</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19283; 34262</t>
+          <t>19322; 34130</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19631; 35200</t>
+          <t>20196; 34858</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>20858; 34537</t>
+          <t>20446; 34895</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>848; 6174</t>
+          <t>870; 6178</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>205</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>191</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>184</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>117075</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>130188</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>123898</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>23040</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>134830</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>131844</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>118480</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>17594</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>117075</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>130188</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>123898</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>24386</t>
+          <t>17877</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>41980</t>
+          <t>40917</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>120188; 151149</t>
+          <t>104037; 133551</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>115642; 149401</t>
+          <t>113405; 148545</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>103932; 134314</t>
+          <t>108725; 140706</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12163; 24991</t>
+          <t>16424; 31278</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>102815; 134049</t>
+          <t>119089; 150412</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>113380; 147430</t>
+          <t>116413; 150332</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>106878; 140542</t>
+          <t>103394; 133773</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>16772; 32749</t>
+          <t>12402; 25046</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>231118; 276975</t>
+          <t>229633; 276847</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>237633; 286527</t>
+          <t>238706; 287430</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>219462; 265619</t>
+          <t>221542; 265152</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>32890; 52155</t>
+          <t>32088; 51802</t>
         </is>
       </c>
     </row>
